--- a/clustering/sepsectors/research sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/research sector (VDS_s) 0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="17">
   <si>
     <t>sector</t>
   </si>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120.28515625" customWidth="1"/>
@@ -789,7 +789,7 @@
         <v>1093853.40159167</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>14</v>
       </c>
@@ -810,7 +810,7 @@
         <v>2.5947743971152693E-3</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
@@ -831,7 +831,7 @@
         <v>2.2454820234090326E-3</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>16</v>
       </c>
@@ -850,6 +850,540 @@
       <c r="G20" s="3">
         <f t="shared" si="2"/>
         <v>1.1555534045986038</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2312764.5271400302</v>
+      </c>
+      <c r="E25" s="3">
+        <v>35420.059524999997</v>
+      </c>
+      <c r="F25" s="4">
+        <v>5.6205038026400662E-3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1.8864917830766969E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2056038.0691327541</v>
+      </c>
+      <c r="E26" s="3">
+        <v>35306.169047820003</v>
+      </c>
+      <c r="F26" s="4">
+        <v>7.4585983781851224E-3</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.5495337612500891E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1713109.9518803279</v>
+      </c>
+      <c r="E27" s="3">
+        <v>77023.192478700003</v>
+      </c>
+      <c r="F27" s="4">
+        <v>9.4864560705148846E-3</v>
+      </c>
+      <c r="G27" s="4">
+        <v>3.0572532777723999E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1230284.2821290109</v>
+      </c>
+      <c r="E28" s="3">
+        <v>94580.340012330009</v>
+      </c>
+      <c r="F28" s="4">
+        <v>4.1181927359240046E-3</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2.9431664964802489E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="3">
+        <f>AVERAGE(D25:D26)</f>
+        <v>2184401.2981363921</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" ref="E30:G30" si="3">AVERAGE(E25:E26)</f>
+        <v>35363.114286409997</v>
+      </c>
+      <c r="F30" s="5">
+        <f t="shared" si="3"/>
+        <v>6.5395510904125943E-3</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" si="3"/>
+        <v>1.718012772163393E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3">
+        <f>AVERAGE(D27:D28)</f>
+        <v>1471697.1170046693</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" ref="E31:G31" si="4">AVERAGE(E27:E28)</f>
+        <v>85801.766245514998</v>
+      </c>
+      <c r="F31" s="5">
+        <f t="shared" si="4"/>
+        <v>6.8023244032194442E-3</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" si="4"/>
+        <v>3.0002098871263244E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="3">
+        <f>D30/D31</f>
+        <v>1.4842736816541999</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" ref="E33:G33" si="5">E30/E31</f>
+        <v>0.4121490248256805</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="5"/>
+        <v>0.96137007040086431</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57263086143914699</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1177149.00870383</v>
+      </c>
+      <c r="E36" s="3">
+        <v>54257.120220599987</v>
+      </c>
+      <c r="F36" s="4">
+        <v>3.1222927114860181E-2</v>
+      </c>
+      <c r="G36" s="4">
+        <v>4.4066793598312361E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1104497.8864203531</v>
+      </c>
+      <c r="E37" s="3">
+        <v>55926.329561999992</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1.456969533637424E-2</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1.725521704280945E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1083208.9167629869</v>
+      </c>
+      <c r="E38" s="3">
+        <v>110639.49239553</v>
+      </c>
+      <c r="F38" s="4">
+        <v>6.9333248439685724E-3</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1.1143475296256969E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1077864.821598877</v>
+      </c>
+      <c r="E39" s="3">
+        <v>73997.227386940009</v>
+      </c>
+      <c r="F39" s="4">
+        <v>9.7692142174449353E-3</v>
+      </c>
+      <c r="G39" s="4">
+        <v>9.558347653642385E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="3">
+        <f>AVERAGE(D36:D37)</f>
+        <v>1140823.4475620915</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" ref="E41:G41" si="6">AVERAGE(E36:E37)</f>
+        <v>55091.724891299993</v>
+      </c>
+      <c r="F41" s="5">
+        <f t="shared" si="6"/>
+        <v>2.2896311225617211E-2</v>
+      </c>
+      <c r="G41" s="5">
+        <f t="shared" si="6"/>
+        <v>3.0661005320560906E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="3">
+        <f>AVERAGE(D38:D39)</f>
+        <v>1080536.8691809319</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" ref="E42:G42" si="7">AVERAGE(E38:E39)</f>
+        <v>92318.359891235013</v>
+      </c>
+      <c r="F42" s="5">
+        <f t="shared" si="7"/>
+        <v>8.3512695307067543E-3</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="7"/>
+        <v>5.3363475916340412E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="3">
+        <f>D41/D42</f>
+        <v>1.0557931710621387</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" ref="E44:G44" si="8">E41/E42</f>
+        <v>0.59675805501967727</v>
+      </c>
+      <c r="F44" s="3">
+        <f t="shared" si="8"/>
+        <v>2.741656360321008</v>
+      </c>
+      <c r="G44" s="3">
+        <f t="shared" si="8"/>
+        <v>0.57456911856021375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D47" s="3">
+        <v>729412.67096789309</v>
+      </c>
+      <c r="E47" s="3">
+        <v>60313.34351775</v>
+      </c>
+      <c r="F47" s="4">
+        <v>3.7694938920620688E-4</v>
+      </c>
+      <c r="G47" s="4">
+        <v>1.654533485954597E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D48" s="3">
+        <v>648447.24948227091</v>
+      </c>
+      <c r="E48" s="3">
+        <v>22130.276711350001</v>
+      </c>
+      <c r="F48" s="4">
+        <v>1.068848483528837E-2</v>
+      </c>
+      <c r="G48" s="4">
+        <v>8.5913209572516789E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D49" s="3">
+        <v>647963.01508706179</v>
+      </c>
+      <c r="E49" s="3">
+        <v>30679.58334573</v>
+      </c>
+      <c r="F49" s="4">
+        <v>6.9744795028248326E-4</v>
+      </c>
+      <c r="G49" s="4">
+        <v>1.104087647419581E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D50" s="3">
+        <v>585416.38894337451</v>
+      </c>
+      <c r="E50" s="3">
+        <v>80201.013479729998</v>
+      </c>
+      <c r="F50" s="4">
+        <v>3.0546519921711193E-4</v>
+      </c>
+      <c r="G50" s="4">
+        <v>1.7612261076438901E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="3">
+        <f>AVERAGE(D47:D48)</f>
+        <v>688929.960225082</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" ref="E52:G52" si="9">AVERAGE(E47:E48)</f>
+        <v>41221.810114549997</v>
+      </c>
+      <c r="F52" s="5">
+        <f t="shared" si="9"/>
+        <v>5.5327171122472882E-3</v>
+      </c>
+      <c r="G52" s="5">
+        <f t="shared" si="9"/>
+        <v>1.2568327908398826E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3">
+        <f>AVERAGE(D49:D50)</f>
+        <v>616689.70201521809</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" ref="E53:G53" si="10">AVERAGE(E49:E50)</f>
+        <v>55440.298412730001</v>
+      </c>
+      <c r="F53" s="5">
+        <f t="shared" si="10"/>
+        <v>5.0145657474979762E-4</v>
+      </c>
+      <c r="G53" s="5">
+        <f t="shared" si="10"/>
+        <v>1.4326568775317356E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C55" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="3">
+        <f>D52/D53</f>
+        <v>1.1171419888702492</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" ref="E55:G55" si="11">E52/E53</f>
+        <v>0.74353514130949905</v>
+      </c>
+      <c r="F55" s="3">
+        <f t="shared" si="11"/>
+        <v>11.033292593696363</v>
+      </c>
+      <c r="G55" s="3">
+        <f t="shared" si="11"/>
+        <v>8.7727411256017351</v>
       </c>
     </row>
   </sheetData>
@@ -857,6 +1391,294 @@
     <sortCondition descending="1" ref="D2:D13"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25:D28">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:E28">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25:F28">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25:G28">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:D31">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30:E31">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:F31">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G31">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D36:D39">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E36:E39">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36:F39">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G36:G39">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D41:D42">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E41:E42">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F41:F42">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G41:G42">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D47:D50">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -868,7 +1690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E47:E50">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -880,7 +1702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F47:F50">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -892,7 +1714,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G47:G50">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -904,7 +1726,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D18">
+  <conditionalFormatting sqref="D52:D53">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -916,7 +1738,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E18">
+  <conditionalFormatting sqref="E52:E53">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -928,7 +1750,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F18">
+  <conditionalFormatting sqref="F52:F53">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -940,7 +1762,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="G52:G53">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/research sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/research sector (VDS_s) 0.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="18">
   <si>
     <t>sector</t>
   </si>
@@ -70,6 +73,9 @@
   </si>
   <si>
     <t>разница</t>
+  </si>
+  <si>
+    <t>Year</t>
   </si>
 </sst>
 </file>
@@ -147,7 +153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -168,6 +174,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -184,6 +193,3072 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>71</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$43</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,53</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$43:$G$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4341128768543896</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96268324181002174</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DDFB-4CE9-9083-54649E465574}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$46:$G$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.37449706271284755</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.59247665944601891</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61705446414673482</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-DDFB-4CE9-9083-54649E465574}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>72</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,92</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$67:$G$67</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$68:$G$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.66881387273907633</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.31288591814299799</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-139E-4DBE-A1DE-B0BB06A7FA1E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$71</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$67:$G$67</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$71:$G$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.490395599670991</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.46102940795964764</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-139E-4DBE-A1DE-B0BB06A7FA1E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>73</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$94</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,80</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$67:$G$67</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$94:$G$94</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8578905609577977E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.10644850180398349</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D4A3-43D7-9754-076BD54858B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$97</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$67:$G$67</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$97:$G$97</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75202719892054226</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5266868505225042E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D4A3-43D7-9754-076BD54858B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>503465</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>470531</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>135779</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>17319</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>17318</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>40050</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>153097</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>517071</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>539802</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>40529</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Original"/>
+      <sheetName val="Only best"/>
+      <sheetName val="Best|Worst"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="89">
+          <cell r="D89" t="str">
+            <v>Year</v>
+          </cell>
+          <cell r="E89" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F89" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G89" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="C90">
+            <v>0.60541707637600206</v>
+          </cell>
+          <cell r="D90">
+            <v>0.75</v>
+          </cell>
+          <cell r="E90">
+            <v>1</v>
+          </cell>
+          <cell r="F90">
+            <v>0.80661939562538798</v>
+          </cell>
+          <cell r="G90">
+            <v>0.45477225885659545</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="C91">
+            <v>0.62826451624711255</v>
+          </cell>
+          <cell r="D91">
+            <v>1</v>
+          </cell>
+          <cell r="E91">
+            <v>0.7323973572762863</v>
+          </cell>
+          <cell r="F91">
+            <v>0.9611546957323327</v>
+          </cell>
+          <cell r="G91">
+            <v>0.83771179639168136</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0.78924387345553881</v>
+          </cell>
+          <cell r="D92">
+            <v>0.5</v>
+          </cell>
+          <cell r="E92">
+            <v>0.90624842311195075</v>
+          </cell>
+          <cell r="F92">
+            <v>1</v>
+          </cell>
+          <cell r="G92">
+            <v>0.67809276193519175</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="C93">
+            <v>1</v>
+          </cell>
+          <cell r="D93">
+            <v>0.25</v>
+          </cell>
+          <cell r="E93">
+            <v>0.89882061387652312</v>
+          </cell>
+          <cell r="F93">
+            <v>0.17795127025264079</v>
+          </cell>
+          <cell r="G93">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -471,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120.28515625" customWidth="1"/>
@@ -883,7 +3958,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="2">
-        <v>2024</v>
+        <v>4</v>
       </c>
       <c r="D25" s="3">
         <v>2312764.5271400302</v>
@@ -906,7 +3981,7 @@
         <v>8</v>
       </c>
       <c r="C26" s="2">
-        <v>2023</v>
+        <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>2056038.0691327541</v>
@@ -929,7 +4004,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="2">
-        <v>2022</v>
+        <v>2</v>
       </c>
       <c r="D27" s="3">
         <v>1713109.9518803279</v>
@@ -952,7 +4027,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="2">
-        <v>2021</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3">
         <v>1230284.2821290109</v>
@@ -1009,7 +4084,7 @@
         <v>3.0002098871263244E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C33" s="6" t="s">
         <v>16</v>
       </c>
@@ -1030,365 +4105,1001 @@
         <v>0.57263086143914699</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <f>MAX(C25:C28)</f>
+        <v>4</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" ref="D35:G35" si="6">MAX(D25:D28)</f>
+        <v>2312764.5271400302</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="6"/>
+        <v>94580.340012330009</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="6"/>
+        <v>9.4864560705148846E-3</v>
+      </c>
+      <c r="G35" s="2">
+        <f t="shared" si="6"/>
+        <v>3.0572532777723999E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <f>C25/C$35</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" ref="D37:G37" si="7">D25/D$35</f>
+        <v>1</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.37449706271284755</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.59247665944601891</v>
+      </c>
+      <c r="G37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.61705446414673482</v>
+      </c>
+    </row>
+    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C38" s="2">
+        <f t="shared" ref="C38:G40" si="8">C26/C$35</f>
+        <v>0.75</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.88899585107146872</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.3732928962109599</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.78623653793827153</v>
+      </c>
+      <c r="G38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.50683853134311552</v>
+      </c>
+    </row>
+    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C39" s="2">
+        <f t="shared" si="8"/>
+        <v>0.5</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="8"/>
+        <v>0.74071957251902487</v>
+      </c>
+      <c r="E39" s="2">
+        <f t="shared" si="8"/>
+        <v>0.81436789578742097</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C40" s="2">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="8"/>
+        <v>0.53195397442833625</v>
+      </c>
+      <c r="E40" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" si="8"/>
+        <v>0.4341128768543896</v>
+      </c>
+      <c r="G40" s="2">
+        <f t="shared" si="8"/>
+        <v>0.96268324181002174</v>
+      </c>
+    </row>
+    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="3">
+        <v>0.53195397442833625</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0.4341128768543896</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.96268324181002174</v>
+      </c>
+    </row>
+    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C44" s="3">
+        <v>0.74071957251902487</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.81436789578742097</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C45" s="3">
+        <v>0.88899585107146872</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.3732928962109599</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.78623653793827153</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0.50683853134311552</v>
+      </c>
+    </row>
+    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.37449706271284755</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.59247665944601891</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0.61705446414673482</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D36" s="3">
-        <v>1177149.00870383</v>
-      </c>
-      <c r="E36" s="3">
-        <v>54257.120220599987</v>
-      </c>
-      <c r="F36" s="4">
-        <v>3.1222927114860181E-2</v>
-      </c>
-      <c r="G36" s="4">
-        <v>4.4066793598312361E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D37" s="3">
-        <v>1104497.8864203531</v>
-      </c>
-      <c r="E37" s="3">
-        <v>55926.329561999992</v>
-      </c>
-      <c r="F37" s="4">
-        <v>1.456969533637424E-2</v>
-      </c>
-      <c r="G37" s="4">
-        <v>1.725521704280945E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1083208.9167629869</v>
-      </c>
-      <c r="E38" s="3">
-        <v>110639.49239553</v>
-      </c>
-      <c r="F38" s="4">
-        <v>6.9333248439685724E-3</v>
-      </c>
-      <c r="G38" s="4">
-        <v>1.1143475296256969E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D39" s="3">
-        <v>1077864.821598877</v>
-      </c>
-      <c r="E39" s="3">
-        <v>73997.227386940009</v>
-      </c>
-      <c r="F39" s="4">
-        <v>9.7692142174449353E-3</v>
-      </c>
-      <c r="G39" s="4">
-        <v>9.558347653642385E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" s="3">
-        <f>AVERAGE(D36:D37)</f>
-        <v>1140823.4475620915</v>
-      </c>
-      <c r="E41" s="3">
-        <f t="shared" ref="E41:G41" si="6">AVERAGE(E36:E37)</f>
-        <v>55091.724891299993</v>
-      </c>
-      <c r="F41" s="5">
-        <f t="shared" si="6"/>
-        <v>2.2896311225617211E-2</v>
-      </c>
-      <c r="G41" s="5">
-        <f t="shared" si="6"/>
-        <v>3.0661005320560906E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="3">
-        <f>AVERAGE(D38:D39)</f>
-        <v>1080536.8691809319</v>
-      </c>
-      <c r="E42" s="3">
-        <f t="shared" ref="E42:G42" si="7">AVERAGE(E38:E39)</f>
-        <v>92318.359891235013</v>
-      </c>
-      <c r="F42" s="5">
-        <f t="shared" si="7"/>
-        <v>8.3512695307067543E-3</v>
-      </c>
-      <c r="G42" s="5">
-        <f t="shared" si="7"/>
-        <v>5.3363475916340412E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C44" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" s="3">
-        <f>D41/D42</f>
-        <v>1.0557931710621387</v>
-      </c>
-      <c r="E44" s="3">
-        <f t="shared" ref="E44:G44" si="8">E41/E42</f>
-        <v>0.59675805501967727</v>
-      </c>
-      <c r="F44" s="3">
-        <f t="shared" si="8"/>
-        <v>2.741656360321008</v>
-      </c>
-      <c r="G44" s="3">
-        <f t="shared" si="8"/>
-        <v>0.57456911856021375</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D47" s="3">
-        <v>729412.67096789309</v>
-      </c>
-      <c r="E47" s="3">
-        <v>60313.34351775</v>
-      </c>
-      <c r="F47" s="4">
-        <v>3.7694938920620688E-4</v>
-      </c>
-      <c r="G47" s="4">
-        <v>1.654533485954597E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D48" s="3">
-        <v>648447.24948227091</v>
-      </c>
-      <c r="E48" s="3">
-        <v>22130.276711350001</v>
-      </c>
-      <c r="F48" s="4">
-        <v>1.068848483528837E-2</v>
-      </c>
-      <c r="G48" s="4">
-        <v>8.5913209572516789E-4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D49" s="3">
-        <v>647963.01508706179</v>
-      </c>
-      <c r="E49" s="3">
-        <v>30679.58334573</v>
-      </c>
-      <c r="F49" s="4">
-        <v>6.9744795028248326E-4</v>
-      </c>
-      <c r="G49" s="4">
-        <v>1.104087647419581E-4</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="2">
+        <v>3</v>
+      </c>
+      <c r="D50" s="3">
+        <v>1177149.00870383</v>
+      </c>
+      <c r="E50" s="3">
+        <v>54257.120220599987</v>
+      </c>
+      <c r="F50" s="4">
+        <v>3.1222927114860181E-2</v>
+      </c>
+      <c r="G50" s="4">
+        <v>4.4066793598312361E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="2">
+        <v>4</v>
+      </c>
+      <c r="D51" s="3">
+        <v>1104497.8864203531</v>
+      </c>
+      <c r="E51" s="3">
+        <v>55926.329561999992</v>
+      </c>
+      <c r="F51" s="4">
+        <v>1.456969533637424E-2</v>
+      </c>
+      <c r="G51" s="4">
+        <v>1.725521704280945E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3">
+        <v>1083208.9167629869</v>
+      </c>
+      <c r="E52" s="3">
+        <v>110639.49239553</v>
+      </c>
+      <c r="F52" s="4">
+        <v>6.9333248439685724E-3</v>
+      </c>
+      <c r="G52" s="4">
+        <v>1.1143475296256969E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2">
+        <v>2</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1077864.821598877</v>
+      </c>
+      <c r="E53" s="3">
+        <v>73997.227386940009</v>
+      </c>
+      <c r="F53" s="4">
+        <v>9.7692142174449353E-3</v>
+      </c>
+      <c r="G53" s="4">
+        <v>9.558347653642385E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3">
+        <f>AVERAGE(D50:D51)</f>
+        <v>1140823.4475620915</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" ref="E55:G55" si="9">AVERAGE(E50:E51)</f>
+        <v>55091.724891299993</v>
+      </c>
+      <c r="F55" s="5">
+        <f t="shared" si="9"/>
+        <v>2.2896311225617211E-2</v>
+      </c>
+      <c r="G55" s="5">
+        <f t="shared" si="9"/>
+        <v>3.0661005320560906E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3">
+        <f>AVERAGE(D52:D53)</f>
+        <v>1080536.8691809319</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" ref="E56:G56" si="10">AVERAGE(E52:E53)</f>
+        <v>92318.359891235013</v>
+      </c>
+      <c r="F56" s="5">
+        <f t="shared" si="10"/>
+        <v>8.3512695307067543E-3</v>
+      </c>
+      <c r="G56" s="5">
+        <f t="shared" si="10"/>
+        <v>5.3363475916340412E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="3">
+        <f>D55/D56</f>
+        <v>1.0557931710621387</v>
+      </c>
+      <c r="E58" s="3">
+        <f t="shared" ref="E58:G58" si="11">E55/E56</f>
+        <v>0.59675805501967727</v>
+      </c>
+      <c r="F58" s="3">
+        <f t="shared" si="11"/>
+        <v>2.741656360321008</v>
+      </c>
+      <c r="G58" s="3">
+        <f t="shared" si="11"/>
+        <v>0.57456911856021375</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C60" s="2">
+        <f>MAX(C50:C53)</f>
+        <v>4</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" ref="D60:G60" si="12">MAX(D50:D53)</f>
+        <v>1177149.00870383</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="12"/>
+        <v>110639.49239553</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="12"/>
+        <v>3.1222927114860181E-2</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="12"/>
+        <v>9.558347653642385E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C61" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C62" s="2">
+        <f>C50/C$60</f>
+        <v>0.75</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" ref="D62:G62" si="13">D50/D$60</f>
+        <v>1</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.490395599670991</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.46102940795964764</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C63" s="2">
+        <f t="shared" ref="C63:G65" si="14">C51/C$60</f>
+        <v>1</v>
+      </c>
+      <c r="D63" s="2">
+        <f t="shared" si="14"/>
+        <v>0.93828213612185452</v>
+      </c>
+      <c r="E63" s="2">
+        <f t="shared" si="14"/>
+        <v>0.50548252121463544</v>
+      </c>
+      <c r="F63" s="2">
+        <f t="shared" si="14"/>
+        <v>0.46663451132485162</v>
+      </c>
+      <c r="G63" s="2">
+        <f t="shared" si="14"/>
+        <v>0.18052510400407995</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C64" s="2">
+        <f t="shared" si="14"/>
+        <v>0.25</v>
+      </c>
+      <c r="D64" s="2">
+        <f t="shared" si="14"/>
+        <v>0.92019694087473147</v>
+      </c>
+      <c r="E64" s="2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="F64" s="2">
+        <f t="shared" si="14"/>
+        <v>0.22205877169885008</v>
+      </c>
+      <c r="G64" s="2">
+        <f t="shared" si="14"/>
+        <v>0.11658369940133473</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="2">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="D65" s="2">
+        <f t="shared" si="14"/>
+        <v>0.91565707793079165</v>
+      </c>
+      <c r="E65" s="2">
+        <f t="shared" si="14"/>
+        <v>0.66881387273907633</v>
+      </c>
+      <c r="F65" s="2">
+        <f t="shared" si="14"/>
+        <v>0.31288591814299799</v>
+      </c>
+      <c r="G65" s="2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C68" s="3">
+        <v>0.91565707793079165</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.66881387273907633</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0.31288591814299799</v>
+      </c>
+      <c r="G68" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C69" s="3">
+        <v>0.92019694087473147</v>
+      </c>
+      <c r="D69" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E69" s="2">
+        <v>1</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0.22205877169885008</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0.11658369940133473</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C70" s="3">
+        <v>0.93828213612185452</v>
+      </c>
+      <c r="D70" s="2">
+        <v>1</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.50548252121463544</v>
+      </c>
+      <c r="F70" s="2">
+        <v>0.46663451132485162</v>
+      </c>
+      <c r="G70" s="2">
+        <v>0.18052510400407995</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C71" s="3">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0.490395599670991</v>
+      </c>
+      <c r="F71" s="2">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2">
+        <v>0.46102940795964764</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B76" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D50" s="3">
+      <c r="C76" s="2">
+        <v>4</v>
+      </c>
+      <c r="D76" s="3">
+        <v>729412.67096789309</v>
+      </c>
+      <c r="E76" s="3">
+        <v>60313.34351775</v>
+      </c>
+      <c r="F76" s="4">
+        <v>3.7694938920620688E-4</v>
+      </c>
+      <c r="G76" s="4">
+        <v>1.654533485954597E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="3">
+        <v>648447.24948227091</v>
+      </c>
+      <c r="E77" s="3">
+        <v>22130.276711350001</v>
+      </c>
+      <c r="F77" s="4">
+        <v>1.068848483528837E-2</v>
+      </c>
+      <c r="G77" s="4">
+        <v>8.5913209572516789E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="2">
+        <v>3</v>
+      </c>
+      <c r="D78" s="3">
+        <v>647963.01508706179</v>
+      </c>
+      <c r="E78" s="3">
+        <v>30679.58334573</v>
+      </c>
+      <c r="F78" s="4">
+        <v>6.9744795028248326E-4</v>
+      </c>
+      <c r="G78" s="4">
+        <v>1.104087647419581E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="2">
+        <v>2</v>
+      </c>
+      <c r="D79" s="3">
         <v>585416.38894337451</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E79" s="3">
         <v>80201.013479729998</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F79" s="4">
         <v>3.0546519921711193E-4</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G79" s="4">
         <v>1.7612261076438901E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="3">
-        <f>AVERAGE(D47:D48)</f>
+      <c r="D81" s="3">
+        <f>AVERAGE(D76:D77)</f>
         <v>688929.960225082</v>
       </c>
-      <c r="E52" s="3">
-        <f t="shared" ref="E52:G52" si="9">AVERAGE(E47:E48)</f>
+      <c r="E81" s="3">
+        <f t="shared" ref="E81:G81" si="15">AVERAGE(E76:E77)</f>
         <v>41221.810114549997</v>
       </c>
-      <c r="F52" s="5">
-        <f t="shared" si="9"/>
+      <c r="F81" s="5">
+        <f t="shared" si="15"/>
         <v>5.5327171122472882E-3</v>
       </c>
-      <c r="G52" s="5">
-        <f t="shared" si="9"/>
+      <c r="G81" s="5">
+        <f t="shared" si="15"/>
         <v>1.2568327908398826E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="3">
-        <f>AVERAGE(D49:D50)</f>
+      <c r="D82" s="3">
+        <f>AVERAGE(D78:D79)</f>
         <v>616689.70201521809</v>
       </c>
-      <c r="E53" s="3">
-        <f t="shared" ref="E53:G53" si="10">AVERAGE(E49:E50)</f>
+      <c r="E82" s="3">
+        <f t="shared" ref="E82:G82" si="16">AVERAGE(E78:E79)</f>
         <v>55440.298412730001</v>
       </c>
-      <c r="F53" s="5">
-        <f t="shared" si="10"/>
+      <c r="F82" s="5">
+        <f t="shared" si="16"/>
         <v>5.0145657474979762E-4</v>
       </c>
-      <c r="G53" s="5">
-        <f t="shared" si="10"/>
+      <c r="G82" s="5">
+        <f t="shared" si="16"/>
         <v>1.4326568775317356E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C55" s="6" t="s">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C84" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="3">
-        <f>D52/D53</f>
+      <c r="D84" s="3">
+        <f>D81/D82</f>
         <v>1.1171419888702492</v>
       </c>
-      <c r="E55" s="3">
-        <f t="shared" ref="E55:G55" si="11">E52/E53</f>
+      <c r="E84" s="3">
+        <f t="shared" ref="E84:G84" si="17">E81/E82</f>
         <v>0.74353514130949905</v>
       </c>
-      <c r="F55" s="3">
-        <f t="shared" si="11"/>
+      <c r="F84" s="3">
+        <f t="shared" si="17"/>
         <v>11.033292593696363</v>
       </c>
-      <c r="G55" s="3">
-        <f t="shared" si="11"/>
+      <c r="G84" s="3">
+        <f t="shared" si="17"/>
         <v>8.7727411256017351</v>
       </c>
     </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C86" s="2">
+        <f>MAX(C76:C79)</f>
+        <v>4</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" ref="D86:G86" si="18">MAX(D76:D79)</f>
+        <v>729412.67096789309</v>
+      </c>
+      <c r="E86" s="2">
+        <f t="shared" si="18"/>
+        <v>80201.013479729998</v>
+      </c>
+      <c r="F86" s="2">
+        <f t="shared" si="18"/>
+        <v>1.068848483528837E-2</v>
+      </c>
+      <c r="G86" s="2">
+        <f t="shared" si="18"/>
+        <v>1.654533485954597E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C87" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C88" s="2">
+        <f>C76/C$86</f>
+        <v>1</v>
+      </c>
+      <c r="D88" s="2">
+        <f t="shared" ref="D88:G88" si="19">D76/D$86</f>
+        <v>1</v>
+      </c>
+      <c r="E88" s="2">
+        <f t="shared" si="19"/>
+        <v>0.75202719892054226</v>
+      </c>
+      <c r="F88" s="2">
+        <f t="shared" si="19"/>
+        <v>3.5266868505225042E-2</v>
+      </c>
+      <c r="G88" s="2">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C89" s="2">
+        <f t="shared" ref="C89:G91" si="20">C77/C$86</f>
+        <v>0.25</v>
+      </c>
+      <c r="D89" s="2">
+        <f t="shared" si="20"/>
+        <v>0.88899915684466346</v>
+      </c>
+      <c r="E89" s="2">
+        <f t="shared" si="20"/>
+        <v>0.27593512539518228</v>
+      </c>
+      <c r="F89" s="2">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="G89" s="2">
+        <f t="shared" si="20"/>
+        <v>0.51925941845140988</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C90" s="2">
+        <f t="shared" si="20"/>
+        <v>0.75</v>
+      </c>
+      <c r="D90" s="2">
+        <f t="shared" si="20"/>
+        <v>0.88833528793412408</v>
+      </c>
+      <c r="E90" s="2">
+        <f t="shared" si="20"/>
+        <v>0.38253361166668992</v>
+      </c>
+      <c r="F90" s="2">
+        <f t="shared" si="20"/>
+        <v>6.5252274857502429E-2</v>
+      </c>
+      <c r="G90" s="2">
+        <f t="shared" si="20"/>
+        <v>6.6731054813470178E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C91" s="2">
+        <f t="shared" si="20"/>
+        <v>0.5</v>
+      </c>
+      <c r="D91" s="2">
+        <f t="shared" si="20"/>
+        <v>0.80258598766396128</v>
+      </c>
+      <c r="E91" s="2">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="F91" s="2">
+        <f t="shared" si="20"/>
+        <v>2.8578905609577977E-2</v>
+      </c>
+      <c r="G91" s="2">
+        <f t="shared" si="20"/>
+        <v>0.10644850180398349</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C93" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C94" s="3">
+        <v>0.80258598766396128</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E94" s="2">
+        <v>1</v>
+      </c>
+      <c r="F94" s="2">
+        <v>2.8578905609577977E-2</v>
+      </c>
+      <c r="G94" s="2">
+        <v>0.10644850180398349</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C95" s="3">
+        <v>0.88833528793412408</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0.38253361166668992</v>
+      </c>
+      <c r="F95" s="2">
+        <v>6.5252274857502429E-2</v>
+      </c>
+      <c r="G95" s="2">
+        <v>6.6731054813470178E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C96" s="3">
+        <v>0.88899915684466346</v>
+      </c>
+      <c r="D96" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0.27593512539518228</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2">
+        <v>0.51925941845140988</v>
+      </c>
+    </row>
+    <row r="97" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C97" s="3">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2">
+        <v>1</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0.75202719892054226</v>
+      </c>
+      <c r="F97" s="2">
+        <v>3.5266868505225042E-2</v>
+      </c>
+      <c r="G97" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:G13">
-    <sortCondition descending="1" ref="D2:D13"/>
+  <sortState ref="C94:G97">
+    <sortCondition ref="C94:C97"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
     <cfRule type="colorScale" priority="32">
@@ -1582,7 +5293,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D36:D39">
+  <conditionalFormatting sqref="D50:D53">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -1594,7 +5305,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E39">
+  <conditionalFormatting sqref="E50:E53">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -1606,7 +5317,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36:F39">
+  <conditionalFormatting sqref="F50:F53">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -1618,7 +5329,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:G39">
+  <conditionalFormatting sqref="G50:G53">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -1630,7 +5341,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D41:D42">
+  <conditionalFormatting sqref="D55:D56">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -1642,7 +5353,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E41:E42">
+  <conditionalFormatting sqref="E55:E56">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -1654,7 +5365,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F41:F42">
+  <conditionalFormatting sqref="F55:F56">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -1666,7 +5377,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G41:G42">
+  <conditionalFormatting sqref="G55:G56">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -1678,7 +5389,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D47:D50">
+  <conditionalFormatting sqref="D76:D79">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -1690,7 +5401,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E47:E50">
+  <conditionalFormatting sqref="E76:E79">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -1702,7 +5413,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F47:F50">
+  <conditionalFormatting sqref="F76:F79">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1714,7 +5425,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G47:G50">
+  <conditionalFormatting sqref="G76:G79">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1726,7 +5437,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D52:D53">
+  <conditionalFormatting sqref="D81:D82">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1738,7 +5449,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:E53">
+  <conditionalFormatting sqref="E81:E82">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1750,7 +5461,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F52:F53">
+  <conditionalFormatting sqref="F81:F82">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1762,7 +5473,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G52:G53">
+  <conditionalFormatting sqref="G81:G82">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1775,5 +5486,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/clustering/sepsectors/research sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/research sector (VDS_s) 0.xlsx
@@ -14,15 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="21">
   <si>
     <t>sector</t>
   </si>
@@ -77,6 +74,15 @@
   <si>
     <t>Year</t>
   </si>
+  <si>
+    <t>best</t>
+  </si>
+  <si>
+    <t>worst</t>
+  </si>
+  <si>
+    <t>сред</t>
+  </si>
 </sst>
 </file>
 
@@ -85,12 +91,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -151,11 +165,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -170,11 +184,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -408,7 +425,7 @@
                   <c:v>0.59247665944601891</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.61705446414673482</c:v>
+                  <c:v>0.50683853134311552</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -688,7 +705,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$68</c:f>
+              <c:f>Sheet1!$C$67</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -711,7 +728,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$D$67:$G$67</c:f>
+              <c:f>Sheet1!$D$66:$G$66</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -731,7 +748,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$68:$G$68</c:f>
+              <c:f>Sheet1!$D$67:$G$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -761,7 +778,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$71</c:f>
+              <c:f>Sheet1!$C$70</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -784,7 +801,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$D$67:$G$67</c:f>
+              <c:f>Sheet1!$D$66:$G$66</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -804,7 +821,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$71:$G$71</c:f>
+              <c:f>Sheet1!$D$70:$G$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1098,7 +1115,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$94</c:f>
+              <c:f>Sheet1!$C$91</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1121,7 +1138,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$D$67:$G$67</c:f>
+              <c:f>Sheet1!$D$66:$G$66</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1141,7 +1158,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$94:$G$94</c:f>
+              <c:f>Sheet1!$D$91:$G$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1171,7 +1188,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$97</c:f>
+              <c:f>Sheet1!$C$94</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1194,7 +1211,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$D$67:$G$67</c:f>
+              <c:f>Sheet1!$D$66:$G$66</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1214,7 +1231,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$97:$G$97</c:f>
+              <c:f>Sheet1!$D$94:$G$94</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3064,16 +3081,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>503465</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>244929</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>470531</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>211995</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>135779</xdr:rowOff>
+      <xdr:rowOff>94958</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3096,16 +3113,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>17319</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>17318</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>466354</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>112568</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>40050</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>489085</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>153097</xdr:rowOff>
+      <xdr:rowOff>57847</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3128,16 +3145,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>517071</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>244928</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>68035</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>539802</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>267659</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>40529</xdr:rowOff>
+      <xdr:rowOff>13314</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3159,106 +3176,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Original"/>
-      <sheetName val="Only best"/>
-      <sheetName val="Best|Worst"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="89">
-          <cell r="D89" t="str">
-            <v>Year</v>
-          </cell>
-          <cell r="E89" t="str">
-            <v>ITcosts_s</v>
-          </cell>
-          <cell r="F89" t="str">
-            <v>skvozcosts_s</v>
-          </cell>
-          <cell r="G89" t="str">
-            <v>trainingcosts_s</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="C90">
-            <v>0.60541707637600206</v>
-          </cell>
-          <cell r="D90">
-            <v>0.75</v>
-          </cell>
-          <cell r="E90">
-            <v>1</v>
-          </cell>
-          <cell r="F90">
-            <v>0.80661939562538798</v>
-          </cell>
-          <cell r="G90">
-            <v>0.45477225885659545</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="C91">
-            <v>0.62826451624711255</v>
-          </cell>
-          <cell r="D91">
-            <v>1</v>
-          </cell>
-          <cell r="E91">
-            <v>0.7323973572762863</v>
-          </cell>
-          <cell r="F91">
-            <v>0.9611546957323327</v>
-          </cell>
-          <cell r="G91">
-            <v>0.83771179639168136</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="C92">
-            <v>0.78924387345553881</v>
-          </cell>
-          <cell r="D92">
-            <v>0.5</v>
-          </cell>
-          <cell r="E92">
-            <v>0.90624842311195075</v>
-          </cell>
-          <cell r="F92">
-            <v>1</v>
-          </cell>
-          <cell r="G92">
-            <v>0.67809276193519175</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="C93">
-            <v>1</v>
-          </cell>
-          <cell r="D93">
-            <v>0.25</v>
-          </cell>
-          <cell r="E93">
-            <v>0.89882061387652312</v>
-          </cell>
-          <cell r="F93">
-            <v>0.17795127025264079</v>
-          </cell>
-          <cell r="G93">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3546,7 +3463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120.28515625" customWidth="1"/>
@@ -4084,7 +4001,7 @@
         <v>3.0002098871263244E-3</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C33" s="6" t="s">
         <v>16</v>
       </c>
@@ -4105,7 +4022,7 @@
         <v>0.57263086143914699</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C35" s="2">
         <f>MAX(C25:C28)</f>
         <v>4</v>
@@ -4127,7 +4044,7 @@
         <v>3.0572532777723999E-3</v>
       </c>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C36" s="8" t="s">
         <v>17</v>
       </c>
@@ -4143,8 +4060,15 @@
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="I36" s="8"/>
+      <c r="J36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C37" s="2">
         <f>C25/C$35</f>
         <v>1</v>
@@ -4165,8 +4089,17 @@
         <f t="shared" si="7"/>
         <v>0.61705446414673482</v>
       </c>
-    </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="I37" s="8">
+        <v>71</v>
+      </c>
+      <c r="J37" s="9">
+        <v>0.78951133158097364</v>
+      </c>
+      <c r="K37" s="9">
+        <v>0.6713484394542768</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C38" s="2">
         <f t="shared" ref="C38:G40" si="8">C26/C$35</f>
         <v>0.75</v>
@@ -4187,8 +4120,17 @@
         <f t="shared" si="8"/>
         <v>0.50683853134311552</v>
       </c>
-    </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="I38" s="8">
+        <v>72</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0.8324968816768088</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0.6782776485756381</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C39" s="2">
         <f t="shared" si="8"/>
         <v>0.5</v>
@@ -4209,8 +4151,17 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="I39" s="8">
+        <v>73</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0.90690785588122536</v>
+      </c>
+      <c r="K39" s="3">
+        <v>0.29242266909845338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C40" s="2">
         <f t="shared" si="8"/>
         <v>0.25</v>
@@ -4232,7 +4183,20 @@
         <v>0.96268324181002174</v>
       </c>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="3">
+        <f>AVERAGE(J37:J39)</f>
+        <v>0.84297202304633601</v>
+      </c>
+      <c r="K41" s="3">
+        <f>AVERAGE(K37:K39)</f>
+        <v>0.54734958570945613</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C42" s="8" t="s">
         <v>3</v>
       </c>
@@ -4249,7 +4213,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C43" s="3">
         <v>0.53195397442833625</v>
       </c>
@@ -4266,7 +4230,7 @@
         <v>0.96268324181002174</v>
       </c>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C44" s="3">
         <v>0.74071957251902487</v>
       </c>
@@ -4283,7 +4247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C45" s="3">
         <v>0.88899585107146872</v>
       </c>
@@ -4300,7 +4264,7 @@
         <v>0.50683853134311552</v>
       </c>
     </row>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C46" s="3">
         <v>1</v>
       </c>
@@ -4314,33 +4278,56 @@
         <v>0.59247665944601891</v>
       </c>
       <c r="G46" s="2">
-        <v>0.61705446414673482</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+        <v>0.50683853134311552</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2">
+        <v>3</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1177149.00870383</v>
+      </c>
+      <c r="E49" s="3">
+        <v>54257.120220599987</v>
+      </c>
+      <c r="F49" s="4">
+        <v>3.1222927114860181E-2</v>
+      </c>
+      <c r="G49" s="4">
+        <v>4.4066793598312361E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>9</v>
       </c>
@@ -4348,22 +4335,22 @@
         <v>10</v>
       </c>
       <c r="C50" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" s="3">
-        <v>1177149.00870383</v>
+        <v>1104497.8864203531</v>
       </c>
       <c r="E50" s="3">
-        <v>54257.120220599987</v>
+        <v>55926.329561999992</v>
       </c>
       <c r="F50" s="4">
-        <v>3.1222927114860181E-2</v>
+        <v>1.456969533637424E-2</v>
       </c>
       <c r="G50" s="4">
-        <v>4.4066793598312361E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.725521704280945E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>9</v>
       </c>
@@ -4371,22 +4358,22 @@
         <v>10</v>
       </c>
       <c r="C51" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51" s="3">
-        <v>1104497.8864203531</v>
+        <v>1083208.9167629869</v>
       </c>
       <c r="E51" s="3">
-        <v>55926.329561999992</v>
+        <v>110639.49239553</v>
       </c>
       <c r="F51" s="4">
-        <v>1.456969533637424E-2</v>
+        <v>6.9333248439685724E-3</v>
       </c>
       <c r="G51" s="4">
-        <v>1.725521704280945E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.1143475296256969E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>9</v>
       </c>
@@ -4394,340 +4381,407 @@
         <v>10</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" s="3">
-        <v>1083208.9167629869</v>
+        <v>1077864.821598877</v>
       </c>
       <c r="E52" s="3">
-        <v>110639.49239553</v>
+        <v>73997.227386940009</v>
       </c>
       <c r="F52" s="4">
-        <v>6.9333248439685724E-3</v>
+        <v>9.7692142174449353E-3</v>
       </c>
       <c r="G52" s="4">
-        <v>1.1143475296256969E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="2">
-        <v>2</v>
-      </c>
-      <c r="D53" s="3">
-        <v>1077864.821598877</v>
-      </c>
-      <c r="E53" s="3">
-        <v>73997.227386940009</v>
-      </c>
-      <c r="F53" s="4">
-        <v>9.7692142174449353E-3</v>
-      </c>
-      <c r="G53" s="4">
         <v>9.558347653642385E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B55" s="6" t="s">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="3">
-        <f>AVERAGE(D50:D51)</f>
+      <c r="D54" s="3">
+        <f>AVERAGE(D49:D50)</f>
         <v>1140823.4475620915</v>
       </c>
-      <c r="E55" s="3">
-        <f t="shared" ref="E55:G55" si="9">AVERAGE(E50:E51)</f>
+      <c r="E54" s="3">
+        <f t="shared" ref="E54:G54" si="9">AVERAGE(E49:E50)</f>
         <v>55091.724891299993</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F54" s="5">
         <f t="shared" si="9"/>
         <v>2.2896311225617211E-2</v>
       </c>
-      <c r="G55" s="5">
+      <c r="G54" s="5">
         <f t="shared" si="9"/>
         <v>3.0661005320560906E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B56" s="6" t="s">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B55" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="3">
-        <f>AVERAGE(D52:D53)</f>
+      <c r="D55" s="3">
+        <f>AVERAGE(D51:D52)</f>
         <v>1080536.8691809319</v>
       </c>
-      <c r="E56" s="3">
-        <f t="shared" ref="E56:G56" si="10">AVERAGE(E52:E53)</f>
+      <c r="E55" s="3">
+        <f t="shared" ref="E55:G55" si="10">AVERAGE(E51:E52)</f>
         <v>92318.359891235013</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F55" s="5">
         <f t="shared" si="10"/>
         <v>8.3512695307067543E-3</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G55" s="5">
         <f t="shared" si="10"/>
         <v>5.3363475916340412E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C58" s="6" t="s">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C57" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D58" s="3">
-        <f>D55/D56</f>
+      <c r="D57" s="3">
+        <f>D54/D55</f>
         <v>1.0557931710621387</v>
       </c>
-      <c r="E58" s="3">
-        <f t="shared" ref="E58:G58" si="11">E55/E56</f>
+      <c r="E57" s="3">
+        <f t="shared" ref="E57:G57" si="11">E54/E55</f>
         <v>0.59675805501967727</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F57" s="3">
         <f t="shared" si="11"/>
         <v>2.741656360321008</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G57" s="3">
         <f t="shared" si="11"/>
         <v>0.57456911856021375</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C60" s="2">
-        <f>MAX(C50:C53)</f>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C59" s="2">
+        <f>MAX(C49:C52)</f>
         <v>4</v>
       </c>
-      <c r="D60" s="2">
-        <f t="shared" ref="D60:G60" si="12">MAX(D50:D53)</f>
+      <c r="D59" s="2">
+        <f t="shared" ref="D59:G59" si="12">MAX(D49:D52)</f>
         <v>1177149.00870383</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E59" s="2">
         <f t="shared" si="12"/>
         <v>110639.49239553</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F59" s="2">
         <f t="shared" si="12"/>
         <v>3.1222927114860181E-2</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G59" s="2">
         <f t="shared" si="12"/>
         <v>9.558347653642385E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C61" s="8" t="s">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C60" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D60" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="G60" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J60" s="2"/>
+      <c r="K60" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="2">
+        <f>C49/C$59</f>
+        <v>0.75</v>
+      </c>
+      <c r="D61" s="2">
+        <f>D49/D$59</f>
+        <v>1</v>
+      </c>
+      <c r="E61" s="2">
+        <f>E49/E$59</f>
+        <v>0.490395599670991</v>
+      </c>
+      <c r="F61" s="2">
+        <f>F49/F$59</f>
+        <v>1</v>
+      </c>
+      <c r="G61" s="2">
+        <f>G49/G$59</f>
+        <v>0.46102940795964764</v>
+      </c>
+      <c r="J61" s="8">
+        <v>71</v>
+      </c>
+      <c r="K61" s="3">
+        <f>0.5*(D46*E46+E46*F46+F46*G46+G46*D46)</f>
+        <v>0.70175318133655629</v>
+      </c>
+      <c r="L61" s="3">
+        <f>0.5*(D43*E43+E43*F43+F43*G43+G43*D43)</f>
+        <v>0.6713484394542768</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C62" s="2">
-        <f>C50/C$60</f>
-        <v>0.75</v>
+        <f>C50/C$59</f>
+        <v>1</v>
       </c>
       <c r="D62" s="2">
-        <f t="shared" ref="D62:G62" si="13">D50/D$60</f>
+        <f>D50/D$59</f>
+        <v>0.93828213612185452</v>
+      </c>
+      <c r="E62" s="2">
+        <f>E50/E$59</f>
+        <v>0.50548252121463544</v>
+      </c>
+      <c r="F62" s="2">
+        <f>F50/F$59</f>
+        <v>0.46663451132485162</v>
+      </c>
+      <c r="G62" s="2">
+        <f>G50/G$59</f>
+        <v>0.18052510400407995</v>
+      </c>
+      <c r="J62" s="8"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C63" s="2">
+        <f>C51/C$59</f>
+        <v>0.25</v>
+      </c>
+      <c r="D63" s="2">
+        <f>D51/D$59</f>
+        <v>0.92019694087473147</v>
+      </c>
+      <c r="E63" s="2">
+        <f>E51/E$59</f>
         <v>1</v>
       </c>
-      <c r="E62" s="2">
-        <f t="shared" si="13"/>
-        <v>0.490395599670991</v>
-      </c>
-      <c r="F62" s="2">
-        <f t="shared" si="13"/>
+      <c r="F63" s="2">
+        <f>F51/F$59</f>
+        <v>0.22205877169885008</v>
+      </c>
+      <c r="G63" s="2">
+        <f>G51/G$59</f>
+        <v>0.11658369940133473</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="2">
+        <f>C52/C$59</f>
+        <v>0.5</v>
+      </c>
+      <c r="D64" s="2">
+        <f>D52/D$59</f>
+        <v>0.91565707793079165</v>
+      </c>
+      <c r="E64" s="2">
+        <f>E52/E$59</f>
+        <v>0.66881387273907633</v>
+      </c>
+      <c r="F64" s="2">
+        <f>F52/F$59</f>
+        <v>0.31288591814299799</v>
+      </c>
+      <c r="G64" s="2">
+        <f>G52/G$59</f>
         <v>1</v>
       </c>
-      <c r="G62" s="2">
-        <f t="shared" si="13"/>
-        <v>0.46102940795964764</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C63" s="2">
-        <f t="shared" ref="C63:G65" si="14">C51/C$60</f>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C66" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="3">
+        <v>0.91565707793079165</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.66881387273907633</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0.31288591814299799</v>
+      </c>
+      <c r="G67" s="2">
         <v>1</v>
-      </c>
-      <c r="D63" s="2">
-        <f t="shared" si="14"/>
-        <v>0.93828213612185452</v>
-      </c>
-      <c r="E63" s="2">
-        <f t="shared" si="14"/>
-        <v>0.50548252121463544</v>
-      </c>
-      <c r="F63" s="2">
-        <f t="shared" si="14"/>
-        <v>0.46663451132485162</v>
-      </c>
-      <c r="G63" s="2">
-        <f t="shared" si="14"/>
-        <v>0.18052510400407995</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C64" s="2">
-        <f t="shared" si="14"/>
-        <v>0.25</v>
-      </c>
-      <c r="D64" s="2">
-        <f t="shared" si="14"/>
-        <v>0.92019694087473147</v>
-      </c>
-      <c r="E64" s="2">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="F64" s="2">
-        <f t="shared" si="14"/>
-        <v>0.22205877169885008</v>
-      </c>
-      <c r="G64" s="2">
-        <f t="shared" si="14"/>
-        <v>0.11658369940133473</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C65" s="2">
-        <f t="shared" si="14"/>
-        <v>0.5</v>
-      </c>
-      <c r="D65" s="2">
-        <f t="shared" si="14"/>
-        <v>0.91565707793079165</v>
-      </c>
-      <c r="E65" s="2">
-        <f t="shared" si="14"/>
-        <v>0.66881387273907633</v>
-      </c>
-      <c r="F65" s="2">
-        <f t="shared" si="14"/>
-        <v>0.31288591814299799</v>
-      </c>
-      <c r="G65" s="2">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C67" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C68" s="3">
-        <v>0.91565707793079165</v>
+        <v>0.92019694087473147</v>
       </c>
       <c r="D68" s="2">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E68" s="2">
-        <v>0.66881387273907633</v>
+        <v>1</v>
       </c>
       <c r="F68" s="2">
-        <v>0.31288591814299799</v>
+        <v>0.22205877169885008</v>
       </c>
       <c r="G68" s="2">
-        <v>1</v>
+        <v>0.11658369940133473</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C69" s="3">
-        <v>0.92019694087473147</v>
+        <v>0.93828213612185452</v>
       </c>
       <c r="D69" s="2">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E69" s="2">
-        <v>1</v>
+        <v>0.50548252121463544</v>
       </c>
       <c r="F69" s="2">
-        <v>0.22205877169885008</v>
+        <v>0.46663451132485162</v>
       </c>
       <c r="G69" s="2">
-        <v>0.11658369940133473</v>
+        <v>0.18052510400407995</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C70" s="3">
-        <v>0.93828213612185452</v>
+        <v>1</v>
       </c>
       <c r="D70" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.490395599670991</v>
+      </c>
+      <c r="F70" s="2">
         <v>1</v>
       </c>
-      <c r="E70" s="2">
-        <v>0.50548252121463544</v>
-      </c>
-      <c r="F70" s="2">
-        <v>0.46663451132485162</v>
-      </c>
       <c r="G70" s="2">
-        <v>0.18052510400407995</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C71" s="3">
+        <v>0.46102940795964764</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D71" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E71" s="2">
-        <v>0.490395599670991</v>
-      </c>
-      <c r="F71" s="2">
+      <c r="C72" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="2">
+        <v>4</v>
+      </c>
+      <c r="D73" s="3">
+        <v>729412.67096789309</v>
+      </c>
+      <c r="E73" s="3">
+        <v>60313.34351775</v>
+      </c>
+      <c r="F73" s="4">
+        <v>3.7694938920620688E-4</v>
+      </c>
+      <c r="G73" s="4">
+        <v>1.654533485954597E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="2">
         <v>1</v>
       </c>
-      <c r="G71" s="2">
-        <v>0.46102940795964764</v>
+      <c r="D74" s="3">
+        <v>648447.24948227091</v>
+      </c>
+      <c r="E74" s="3">
+        <v>22130.276711350001</v>
+      </c>
+      <c r="F74" s="4">
+        <v>1.068848483528837E-2</v>
+      </c>
+      <c r="G74" s="4">
+        <v>8.5913209572516789E-4</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="A75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="2">
         <v>3</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>6</v>
+      <c r="D75" s="3">
+        <v>647963.01508706179</v>
+      </c>
+      <c r="E75" s="3">
+        <v>30679.58334573</v>
+      </c>
+      <c r="F75" s="4">
+        <v>6.9744795028248326E-4</v>
+      </c>
+      <c r="G75" s="4">
+        <v>1.104087647419581E-4</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4738,367 +4792,348 @@
         <v>12</v>
       </c>
       <c r="C76" s="2">
+        <v>2</v>
+      </c>
+      <c r="D76" s="3">
+        <v>585416.38894337451</v>
+      </c>
+      <c r="E76" s="3">
+        <v>80201.013479729998</v>
+      </c>
+      <c r="F76" s="4">
+        <v>3.0546519921711193E-4</v>
+      </c>
+      <c r="G76" s="4">
+        <v>1.7612261076438901E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="3">
+        <f>AVERAGE(D73:D74)</f>
+        <v>688929.960225082</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" ref="E78:G78" si="13">AVERAGE(E73:E74)</f>
+        <v>41221.810114549997</v>
+      </c>
+      <c r="F78" s="5">
+        <f t="shared" si="13"/>
+        <v>5.5327171122472882E-3</v>
+      </c>
+      <c r="G78" s="5">
+        <f t="shared" si="13"/>
+        <v>1.2568327908398826E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="3">
+        <f>AVERAGE(D75:D76)</f>
+        <v>616689.70201521809</v>
+      </c>
+      <c r="E79" s="3">
+        <f t="shared" ref="E79:G79" si="14">AVERAGE(E75:E76)</f>
+        <v>55440.298412730001</v>
+      </c>
+      <c r="F79" s="5">
+        <f t="shared" si="14"/>
+        <v>5.0145657474979762E-4</v>
+      </c>
+      <c r="G79" s="5">
+        <f t="shared" si="14"/>
+        <v>1.4326568775317356E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="3">
+        <f>D78/D79</f>
+        <v>1.1171419888702492</v>
+      </c>
+      <c r="E81" s="3">
+        <f t="shared" ref="E81:G81" si="15">E78/E79</f>
+        <v>0.74353514130949905</v>
+      </c>
+      <c r="F81" s="3">
+        <f t="shared" si="15"/>
+        <v>11.033292593696363</v>
+      </c>
+      <c r="G81" s="3">
+        <f t="shared" si="15"/>
+        <v>8.7727411256017351</v>
+      </c>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="2">
+        <f>MAX(C73:C76)</f>
         <v>4</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D83" s="2">
+        <f t="shared" ref="D83:G83" si="16">MAX(D73:D76)</f>
         <v>729412.67096789309</v>
       </c>
-      <c r="E76" s="3">
-        <v>60313.34351775</v>
-      </c>
-      <c r="F76" s="4">
-        <v>3.7694938920620688E-4</v>
-      </c>
-      <c r="G76" s="4">
+      <c r="E83" s="2">
+        <f t="shared" si="16"/>
+        <v>80201.013479729998</v>
+      </c>
+      <c r="F83" s="2">
+        <f t="shared" si="16"/>
+        <v>1.068848483528837E-2</v>
+      </c>
+      <c r="G83" s="2">
+        <f t="shared" si="16"/>
         <v>1.654533485954597E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77" s="2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C84" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J84" s="2"/>
+      <c r="K84" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L84" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="2">
+        <f>C73/C$83</f>
         <v>1</v>
       </c>
-      <c r="D77" s="3">
-        <v>648447.24948227091</v>
-      </c>
-      <c r="E77" s="3">
-        <v>22130.276711350001</v>
-      </c>
-      <c r="F77" s="4">
-        <v>1.068848483528837E-2</v>
-      </c>
-      <c r="G77" s="4">
-        <v>8.5913209572516789E-4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="2">
+      <c r="D85" s="2">
+        <f>D73/D$83</f>
+        <v>1</v>
+      </c>
+      <c r="E85" s="2">
+        <f>E73/E$83</f>
+        <v>0.75202719892054226</v>
+      </c>
+      <c r="F85" s="2">
+        <f>F73/F$83</f>
+        <v>3.5266868505225042E-2</v>
+      </c>
+      <c r="G85" s="2">
+        <f>G73/G$83</f>
+        <v>1</v>
+      </c>
+      <c r="J85" s="8">
+        <v>72</v>
+      </c>
+      <c r="K85" s="3">
+        <f>0.5*(D70*E70+E70*F70+F70*G70+G70*D70)</f>
+        <v>0.8324968816768088</v>
+      </c>
+      <c r="L85" s="3">
+        <f>0.5*(D67*E67+E67*F67+F67*G67+G67*D67)</f>
+        <v>0.6782776485756381</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C86" s="2">
+        <f>C74/C$83</f>
+        <v>0.25</v>
+      </c>
+      <c r="D86" s="2">
+        <f>D74/D$83</f>
+        <v>0.88899915684466346</v>
+      </c>
+      <c r="E86" s="2">
+        <f>E74/E$83</f>
+        <v>0.27593512539518228</v>
+      </c>
+      <c r="F86" s="2">
+        <f>F74/F$83</f>
+        <v>1</v>
+      </c>
+      <c r="G86" s="2">
+        <f>G74/G$83</f>
+        <v>0.51925941845140988</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="2">
+        <f>C75/C$83</f>
+        <v>0.75</v>
+      </c>
+      <c r="D87" s="2">
+        <f>D75/D$83</f>
+        <v>0.88833528793412408</v>
+      </c>
+      <c r="E87" s="2">
+        <f>E75/E$83</f>
+        <v>0.38253361166668992</v>
+      </c>
+      <c r="F87" s="2">
+        <f>F75/F$83</f>
+        <v>6.5252274857502429E-2</v>
+      </c>
+      <c r="G87" s="2">
+        <f>G75/G$83</f>
+        <v>6.6731054813470178E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="2">
+        <f>C76/C$83</f>
+        <v>0.5</v>
+      </c>
+      <c r="D88" s="2">
+        <f>D76/D$83</f>
+        <v>0.80258598766396128</v>
+      </c>
+      <c r="E88" s="2">
+        <f>E76/E$83</f>
+        <v>1</v>
+      </c>
+      <c r="F88" s="2">
+        <f>F76/F$83</f>
+        <v>2.8578905609577977E-2</v>
+      </c>
+      <c r="G88" s="2">
+        <f>G76/G$83</f>
+        <v>0.10644850180398349</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C90" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D78" s="3">
-        <v>647963.01508706179</v>
-      </c>
-      <c r="E78" s="3">
-        <v>30679.58334573</v>
-      </c>
-      <c r="F78" s="4">
-        <v>6.9744795028248326E-4</v>
-      </c>
-      <c r="G78" s="4">
-        <v>1.104087647419581E-4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="2">
-        <v>2</v>
-      </c>
-      <c r="D79" s="3">
-        <v>585416.38894337451</v>
-      </c>
-      <c r="E79" s="3">
-        <v>80201.013479729998</v>
-      </c>
-      <c r="F79" s="4">
-        <v>3.0546519921711193E-4</v>
-      </c>
-      <c r="G79" s="4">
-        <v>1.7612261076438901E-4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B81" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" s="3">
-        <f>AVERAGE(D76:D77)</f>
-        <v>688929.960225082</v>
-      </c>
-      <c r="E81" s="3">
-        <f t="shared" ref="E81:G81" si="15">AVERAGE(E76:E77)</f>
-        <v>41221.810114549997</v>
-      </c>
-      <c r="F81" s="5">
-        <f t="shared" si="15"/>
-        <v>5.5327171122472882E-3</v>
-      </c>
-      <c r="G81" s="5">
-        <f t="shared" si="15"/>
-        <v>1.2568327908398826E-3</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="3">
-        <f>AVERAGE(D78:D79)</f>
-        <v>616689.70201521809</v>
-      </c>
-      <c r="E82" s="3">
-        <f t="shared" ref="E82:G82" si="16">AVERAGE(E78:E79)</f>
-        <v>55440.298412730001</v>
-      </c>
-      <c r="F82" s="5">
-        <f t="shared" si="16"/>
-        <v>5.0145657474979762E-4</v>
-      </c>
-      <c r="G82" s="5">
-        <f t="shared" si="16"/>
-        <v>1.4326568775317356E-4</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C84" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" s="3">
-        <f>D81/D82</f>
-        <v>1.1171419888702492</v>
-      </c>
-      <c r="E84" s="3">
-        <f t="shared" ref="E84:G84" si="17">E81/E82</f>
-        <v>0.74353514130949905</v>
-      </c>
-      <c r="F84" s="3">
-        <f t="shared" si="17"/>
-        <v>11.033292593696363</v>
-      </c>
-      <c r="G84" s="3">
-        <f t="shared" si="17"/>
-        <v>8.7727411256017351</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C86" s="2">
-        <f>MAX(C76:C79)</f>
+      <c r="D90" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D86" s="2">
-        <f t="shared" ref="D86:G86" si="18">MAX(D76:D79)</f>
-        <v>729412.67096789309</v>
-      </c>
-      <c r="E86" s="2">
-        <f t="shared" si="18"/>
-        <v>80201.013479729998</v>
-      </c>
-      <c r="F86" s="2">
-        <f t="shared" si="18"/>
-        <v>1.068848483528837E-2</v>
-      </c>
-      <c r="G86" s="2">
-        <f t="shared" si="18"/>
-        <v>1.654533485954597E-3</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C87" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F87" s="1" t="s">
+      <c r="F90" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="G90" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C88" s="2">
-        <f>C76/C$86</f>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C91" s="3">
+        <v>0.80258598766396128</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E91" s="2">
         <v>1</v>
       </c>
-      <c r="D88" s="2">
-        <f t="shared" ref="D88:G88" si="19">D76/D$86</f>
+      <c r="F91" s="2">
+        <v>2.8578905609577977E-2</v>
+      </c>
+      <c r="G91" s="2">
+        <v>0.10644850180398349</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C92" s="3">
+        <v>0.88833528793412408</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.38253361166668992</v>
+      </c>
+      <c r="F92" s="2">
+        <v>6.5252274857502429E-2</v>
+      </c>
+      <c r="G92" s="2">
+        <v>6.6731054813470178E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C93" s="3">
+        <v>0.88899915684466346</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.27593512539518228</v>
+      </c>
+      <c r="F93" s="2">
         <v>1</v>
       </c>
-      <c r="E88" s="2">
-        <f t="shared" si="19"/>
+      <c r="G93" s="2">
+        <v>0.51925941845140988</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2">
+        <v>1</v>
+      </c>
+      <c r="E94" s="2">
         <v>0.75202719892054226</v>
       </c>
-      <c r="F88" s="2">
-        <f t="shared" si="19"/>
+      <c r="F94" s="2">
         <v>3.5266868505225042E-2</v>
       </c>
-      <c r="G88" s="2">
-        <f t="shared" si="19"/>
+      <c r="G94" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C89" s="2">
-        <f t="shared" ref="C89:G91" si="20">C77/C$86</f>
-        <v>0.25</v>
-      </c>
-      <c r="D89" s="2">
-        <f t="shared" si="20"/>
-        <v>0.88899915684466346</v>
-      </c>
-      <c r="E89" s="2">
-        <f t="shared" si="20"/>
-        <v>0.27593512539518228</v>
-      </c>
-      <c r="F89" s="2">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="G89" s="2">
-        <f t="shared" si="20"/>
-        <v>0.51925941845140988</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C90" s="2">
-        <f t="shared" si="20"/>
-        <v>0.75</v>
-      </c>
-      <c r="D90" s="2">
-        <f t="shared" si="20"/>
-        <v>0.88833528793412408</v>
-      </c>
-      <c r="E90" s="2">
-        <f t="shared" si="20"/>
-        <v>0.38253361166668992</v>
-      </c>
-      <c r="F90" s="2">
-        <f t="shared" si="20"/>
-        <v>6.5252274857502429E-2</v>
-      </c>
-      <c r="G90" s="2">
-        <f t="shared" si="20"/>
-        <v>6.6731054813470178E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C91" s="2">
-        <f t="shared" si="20"/>
-        <v>0.5</v>
-      </c>
-      <c r="D91" s="2">
-        <f t="shared" si="20"/>
-        <v>0.80258598766396128</v>
-      </c>
-      <c r="E91" s="2">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F91" s="2">
-        <f t="shared" si="20"/>
-        <v>2.8578905609577977E-2</v>
-      </c>
-      <c r="G91" s="2">
-        <f t="shared" si="20"/>
-        <v>0.10644850180398349</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C93" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G93" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C94" s="3">
-        <v>0.80258598766396128</v>
-      </c>
-      <c r="D94" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E94" s="2">
-        <v>1</v>
-      </c>
-      <c r="F94" s="2">
-        <v>2.8578905609577977E-2</v>
-      </c>
-      <c r="G94" s="2">
-        <v>0.10644850180398349</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C95" s="3">
-        <v>0.88833528793412408</v>
-      </c>
-      <c r="D95" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E95" s="2">
-        <v>0.38253361166668992</v>
-      </c>
-      <c r="F95" s="2">
-        <v>6.5252274857502429E-2</v>
-      </c>
-      <c r="G95" s="2">
-        <v>6.6731054813470178E-2</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C96" s="3">
-        <v>0.88899915684466346</v>
-      </c>
-      <c r="D96" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E96" s="2">
-        <v>0.27593512539518228</v>
-      </c>
-      <c r="F96" s="2">
-        <v>1</v>
-      </c>
-      <c r="G96" s="2">
-        <v>0.51925941845140988</v>
-      </c>
-    </row>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C97" s="3">
-        <v>1</v>
-      </c>
-      <c r="D97" s="2">
-        <v>1</v>
-      </c>
-      <c r="E97" s="2">
-        <v>0.75202719892054226</v>
-      </c>
-      <c r="F97" s="2">
-        <v>3.5266868505225042E-2</v>
-      </c>
-      <c r="G97" s="2">
-        <v>1</v>
-      </c>
+    <row r="108" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J108" s="2"/>
+      <c r="K108" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L108" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J109" s="8">
+        <v>73</v>
+      </c>
+      <c r="K109" s="3">
+        <f>0.5*(D94*E94+E94*F94+F94*G94+G94*D94)</f>
+        <v>0.90690785588122536</v>
+      </c>
+      <c r="L109" s="3">
+        <f>0.5*(D91*E91+E91*F91+F91*G91+G91*D91)</f>
+        <v>0.29242266909845338</v>
+      </c>
+    </row>
+    <row r="110" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J110" s="2"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+    </row>
+    <row r="111" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J111" s="8"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
     </row>
   </sheetData>
-  <sortState ref="C94:G97">
+  <sortState ref="C91:G94">
     <sortCondition ref="C94:C97"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
@@ -5293,7 +5328,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D50:D53">
+  <conditionalFormatting sqref="D49:D52">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -5305,7 +5340,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E50:E53">
+  <conditionalFormatting sqref="E49:E52">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -5317,7 +5352,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F50:F53">
+  <conditionalFormatting sqref="F49:F52">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -5329,7 +5364,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G50:G53">
+  <conditionalFormatting sqref="G49:G52">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -5341,7 +5376,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D55:D56">
+  <conditionalFormatting sqref="D54:D55">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -5353,7 +5388,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E55:E56">
+  <conditionalFormatting sqref="E54:E55">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -5365,7 +5400,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F55:F56">
+  <conditionalFormatting sqref="F54:F55">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -5377,7 +5412,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G55:G56">
+  <conditionalFormatting sqref="G54:G55">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5389,7 +5424,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D76:D79">
+  <conditionalFormatting sqref="D73:D76">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -5401,7 +5436,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E79">
+  <conditionalFormatting sqref="E73:E76">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -5413,7 +5448,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F76:F79">
+  <conditionalFormatting sqref="F73:F76">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -5425,7 +5460,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G76:G79">
+  <conditionalFormatting sqref="G73:G76">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -5437,7 +5472,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D81:D82">
+  <conditionalFormatting sqref="D78:D79">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5449,7 +5484,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E81:E82">
+  <conditionalFormatting sqref="E78:E79">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -5461,7 +5496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F81:F82">
+  <conditionalFormatting sqref="F78:F79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5473,7 +5508,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G81:G82">
+  <conditionalFormatting sqref="G78:G79">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/research sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/research sector (VDS_s) 0.xlsx
@@ -4507,23 +4507,23 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C61" s="2">
-        <f>C49/C$59</f>
+        <f t="shared" ref="C61:G64" si="13">C49/C$59</f>
         <v>0.75</v>
       </c>
       <c r="D61" s="2">
-        <f>D49/D$59</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E61" s="2">
-        <f>E49/E$59</f>
+        <f t="shared" si="13"/>
         <v>0.490395599670991</v>
       </c>
       <c r="F61" s="2">
-        <f>F49/F$59</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G61" s="2">
-        <f>G49/G$59</f>
+        <f t="shared" si="13"/>
         <v>0.46102940795964764</v>
       </c>
       <c r="J61" s="8">
@@ -4540,23 +4540,23 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C62" s="2">
-        <f>C50/C$59</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D62" s="2">
-        <f>D50/D$59</f>
+        <f t="shared" si="13"/>
         <v>0.93828213612185452</v>
       </c>
       <c r="E62" s="2">
-        <f>E50/E$59</f>
+        <f t="shared" si="13"/>
         <v>0.50548252121463544</v>
       </c>
       <c r="F62" s="2">
-        <f>F50/F$59</f>
+        <f t="shared" si="13"/>
         <v>0.46663451132485162</v>
       </c>
       <c r="G62" s="2">
-        <f>G50/G$59</f>
+        <f t="shared" si="13"/>
         <v>0.18052510400407995</v>
       </c>
       <c r="J62" s="8"/>
@@ -4565,45 +4565,45 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C63" s="2">
-        <f>C51/C$59</f>
+        <f t="shared" si="13"/>
         <v>0.25</v>
       </c>
       <c r="D63" s="2">
-        <f>D51/D$59</f>
+        <f t="shared" si="13"/>
         <v>0.92019694087473147</v>
       </c>
       <c r="E63" s="2">
-        <f>E51/E$59</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F63" s="2">
-        <f>F51/F$59</f>
+        <f t="shared" si="13"/>
         <v>0.22205877169885008</v>
       </c>
       <c r="G63" s="2">
-        <f>G51/G$59</f>
+        <f t="shared" si="13"/>
         <v>0.11658369940133473</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C64" s="2">
-        <f>C52/C$59</f>
+        <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
       <c r="D64" s="2">
-        <f>D52/D$59</f>
+        <f t="shared" si="13"/>
         <v>0.91565707793079165</v>
       </c>
       <c r="E64" s="2">
-        <f>E52/E$59</f>
+        <f t="shared" si="13"/>
         <v>0.66881387273907633</v>
       </c>
       <c r="F64" s="2">
-        <f>F52/F$59</f>
+        <f t="shared" si="13"/>
         <v>0.31288591814299799</v>
       </c>
       <c r="G64" s="2">
-        <f>G52/G$59</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -4816,15 +4816,15 @@
         <v>688929.960225082</v>
       </c>
       <c r="E78" s="3">
-        <f t="shared" ref="E78:G78" si="13">AVERAGE(E73:E74)</f>
+        <f t="shared" ref="E78:G78" si="14">AVERAGE(E73:E74)</f>
         <v>41221.810114549997</v>
       </c>
       <c r="F78" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.5327171122472882E-3</v>
       </c>
       <c r="G78" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.2568327908398826E-3</v>
       </c>
     </row>
@@ -4837,15 +4837,15 @@
         <v>616689.70201521809</v>
       </c>
       <c r="E79" s="3">
-        <f t="shared" ref="E79:G79" si="14">AVERAGE(E75:E76)</f>
+        <f t="shared" ref="E79:G79" si="15">AVERAGE(E75:E76)</f>
         <v>55440.298412730001</v>
       </c>
       <c r="F79" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.0145657474979762E-4</v>
       </c>
       <c r="G79" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.4326568775317356E-4</v>
       </c>
     </row>
@@ -4858,15 +4858,15 @@
         <v>1.1171419888702492</v>
       </c>
       <c r="E81" s="3">
-        <f t="shared" ref="E81:G81" si="15">E78/E79</f>
+        <f t="shared" ref="E81:G81" si="16">E78/E79</f>
         <v>0.74353514130949905</v>
       </c>
       <c r="F81" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>11.033292593696363</v>
       </c>
       <c r="G81" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.7727411256017351</v>
       </c>
     </row>
@@ -4876,19 +4876,19 @@
         <v>4</v>
       </c>
       <c r="D83" s="2">
-        <f t="shared" ref="D83:G83" si="16">MAX(D73:D76)</f>
+        <f t="shared" ref="D83:G83" si="17">MAX(D73:D76)</f>
         <v>729412.67096789309</v>
       </c>
       <c r="E83" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>80201.013479729998</v>
       </c>
       <c r="F83" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.068848483528837E-2</v>
       </c>
       <c r="G83" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.654533485954597E-3</v>
       </c>
     </row>
@@ -4918,23 +4918,23 @@
     </row>
     <row r="85" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C85" s="2">
-        <f>C73/C$83</f>
+        <f t="shared" ref="C85:G88" si="18">C73/C$83</f>
         <v>1</v>
       </c>
       <c r="D85" s="2">
-        <f>D73/D$83</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E85" s="2">
-        <f>E73/E$83</f>
+        <f t="shared" si="18"/>
         <v>0.75202719892054226</v>
       </c>
       <c r="F85" s="2">
-        <f>F73/F$83</f>
+        <f t="shared" si="18"/>
         <v>3.5266868505225042E-2</v>
       </c>
       <c r="G85" s="2">
-        <f>G73/G$83</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J85" s="8">
@@ -4951,67 +4951,67 @@
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C86" s="2">
-        <f>C74/C$83</f>
+        <f t="shared" si="18"/>
         <v>0.25</v>
       </c>
       <c r="D86" s="2">
-        <f>D74/D$83</f>
+        <f t="shared" si="18"/>
         <v>0.88899915684466346</v>
       </c>
       <c r="E86" s="2">
-        <f>E74/E$83</f>
+        <f t="shared" si="18"/>
         <v>0.27593512539518228</v>
       </c>
       <c r="F86" s="2">
-        <f>F74/F$83</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G86" s="2">
-        <f>G74/G$83</f>
+        <f t="shared" si="18"/>
         <v>0.51925941845140988</v>
       </c>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C87" s="2">
-        <f>C75/C$83</f>
+        <f t="shared" si="18"/>
         <v>0.75</v>
       </c>
       <c r="D87" s="2">
-        <f>D75/D$83</f>
+        <f t="shared" si="18"/>
         <v>0.88833528793412408</v>
       </c>
       <c r="E87" s="2">
-        <f>E75/E$83</f>
+        <f t="shared" si="18"/>
         <v>0.38253361166668992</v>
       </c>
       <c r="F87" s="2">
-        <f>F75/F$83</f>
+        <f t="shared" si="18"/>
         <v>6.5252274857502429E-2</v>
       </c>
       <c r="G87" s="2">
-        <f>G75/G$83</f>
+        <f t="shared" si="18"/>
         <v>6.6731054813470178E-2</v>
       </c>
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C88" s="2">
-        <f>C76/C$83</f>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
       <c r="D88" s="2">
-        <f>D76/D$83</f>
+        <f t="shared" si="18"/>
         <v>0.80258598766396128</v>
       </c>
       <c r="E88" s="2">
-        <f>E76/E$83</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F88" s="2">
-        <f>F76/F$83</f>
+        <f t="shared" si="18"/>
         <v>2.8578905609577977E-2</v>
       </c>
       <c r="G88" s="2">
-        <f>G76/G$83</f>
+        <f t="shared" si="18"/>
         <v>0.10644850180398349</v>
       </c>
     </row>

--- a/clustering/sepsectors/research sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/research sector (VDS_s) 0.xlsx
@@ -9,17 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="21">
   <si>
     <t>sector</t>
   </si>
@@ -1442,6 +1443,1392 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>71</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$43</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,53</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Sheet1 (2)'!$E$42:$G$42</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Sheet1 (2)'!$E$43:$G$43</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Sheet1 (2)'!$E$43:$G$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4341128768543896</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.96268324181002174</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4942-4BDF-B4CA-C15D8E5F257C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$44</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,74</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Sheet1 (2)'!$E$42:$G$42</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Sheet1 (2)'!$E$44:$G$44</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Sheet1 (2)'!$E$44:$G$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.81436789578742097</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4942-4BDF-B4CA-C15D8E5F257C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$45</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,89</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Sheet1 (2)'!$E$42:$G$42</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Sheet1 (2)'!$E$45:$G$45</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Sheet1 (2)'!$E$45:$G$45</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.3732928962109599</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.78623653793827153</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.50683853134311552</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4942-4BDF-B4CA-C15D8E5F257C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Sheet1 (2)'!$E$42:$G$42</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Sheet1 (2)'!$E$46:$G$46</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Sheet1 (2)'!$E$46:$G$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.37449706271284755</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.59247665944601891</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.50683853134311552</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-4942-4BDF-B4CA-C15D8E5F257C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>72</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$67</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,92</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$67:$G$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.66881387273907633</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.31288591814299799</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1253-42C4-96EF-D6EF48891EA1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$70</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$70:$G$70</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.490395599670991</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.46102940795964764</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1253-42C4-96EF-D6EF48891EA1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>73</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$91</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,80</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$91:$G$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8578905609577977E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10644850180398349</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E022-4D4D-A0BC-867D33C677FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$94</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$94:$G$94</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.75202719892054226</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5266868505225042E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E022-4D4D-A0BC-867D33C677FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1562,6 +2949,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
@@ -2573,6 +4080,1521 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3159,6 +6181,105 @@
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>242454</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>126422</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>131123</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>173182</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>121228</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>269670</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>167988</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Диаграмма 6"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>51954</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>546759</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>81396</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Диаграмма 7"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -5524,4 +8645,2066 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L111"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="120.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2312764.5271400302</v>
+      </c>
+      <c r="E2" s="3">
+        <v>35420.059524999997</v>
+      </c>
+      <c r="F2" s="4">
+        <v>5.6205038026400662E-3</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.8864917830766969E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2056038.0691327541</v>
+      </c>
+      <c r="E3" s="3">
+        <v>35306.169047820003</v>
+      </c>
+      <c r="F3" s="4">
+        <v>7.4585983781851224E-3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1.5495337612500891E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1713109.9518803279</v>
+      </c>
+      <c r="E4" s="3">
+        <v>77023.192478700003</v>
+      </c>
+      <c r="F4" s="4">
+        <v>9.4864560705148846E-3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>3.0572532777723999E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1230284.2821290109</v>
+      </c>
+      <c r="E5" s="3">
+        <v>94580.340012330009</v>
+      </c>
+      <c r="F5" s="4">
+        <v>4.1181927359240046E-3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>2.9431664964802489E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1177149.00870383</v>
+      </c>
+      <c r="E6" s="3">
+        <v>54257.120220599987</v>
+      </c>
+      <c r="F6" s="4">
+        <v>3.1222927114860181E-2</v>
+      </c>
+      <c r="G6" s="4">
+        <v>4.4066793598312361E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1104497.8864203531</v>
+      </c>
+      <c r="E7" s="3">
+        <v>55926.329561999992</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1.456969533637424E-2</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1.725521704280945E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1083208.9167629869</v>
+      </c>
+      <c r="E8" s="3">
+        <v>110639.49239553</v>
+      </c>
+      <c r="F8" s="4">
+        <v>6.9333248439685724E-3</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1.1143475296256969E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1077864.821598877</v>
+      </c>
+      <c r="E9" s="3">
+        <v>73997.227386940009</v>
+      </c>
+      <c r="F9" s="4">
+        <v>9.7692142174449353E-3</v>
+      </c>
+      <c r="G9" s="4">
+        <v>9.558347653642385E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D10" s="3">
+        <v>729412.67096789309</v>
+      </c>
+      <c r="E10" s="3">
+        <v>60313.34351775</v>
+      </c>
+      <c r="F10" s="4">
+        <v>3.7694938920620688E-4</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1.654533485954597E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D11" s="3">
+        <v>648447.24948227091</v>
+      </c>
+      <c r="E11" s="3">
+        <v>22130.276711350001</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1.068848483528837E-2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>8.5913209572516789E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D12" s="3">
+        <v>647963.01508706179</v>
+      </c>
+      <c r="E12" s="3">
+        <v>30679.58334573</v>
+      </c>
+      <c r="F12" s="4">
+        <v>6.9744795028248326E-4</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1.104087647419581E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D13" s="3">
+        <v>585416.38894337451</v>
+      </c>
+      <c r="E13" s="3">
+        <v>80201.013479729998</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3.0546519921711193E-4</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1.7612261076438901E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3">
+        <f>MEDIAN(D2:D13)</f>
+        <v>1093853.40159167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="3">
+        <f>AVERAGE(D2:D7)</f>
+        <v>1598973.9542343842</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
+        <v>58752.201807741658</v>
+      </c>
+      <c r="F17" s="5">
+        <f t="shared" si="0"/>
+        <v>1.2079395573083082E-2</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="0"/>
+        <v>2.5947743971152693E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3">
+        <f>AVERAGE(D8:D13)</f>
+        <v>795385.51047374401</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
+        <v>62993.48947283833</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" si="1"/>
+        <v>4.7951477392346132E-3</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="1"/>
+        <v>2.2454820234090326E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="3">
+        <f>D17/D18</f>
+        <v>2.0103131540352179</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" ref="E20:G20" si="2">E17/E18</f>
+        <v>0.93267101567812905</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="2"/>
+        <v>2.5190872586151345</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1555534045986038</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2312764.5271400302</v>
+      </c>
+      <c r="E25" s="3">
+        <v>35420.059524999997</v>
+      </c>
+      <c r="F25" s="4">
+        <v>5.6205038026400662E-3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1.8864917830766969E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2056038.0691327541</v>
+      </c>
+      <c r="E26" s="3">
+        <v>35306.169047820003</v>
+      </c>
+      <c r="F26" s="4">
+        <v>7.4585983781851224E-3</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.5495337612500891E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1713109.9518803279</v>
+      </c>
+      <c r="E27" s="3">
+        <v>77023.192478700003</v>
+      </c>
+      <c r="F27" s="4">
+        <v>9.4864560705148846E-3</v>
+      </c>
+      <c r="G27" s="4">
+        <v>3.0572532777723999E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1230284.2821290109</v>
+      </c>
+      <c r="E28" s="3">
+        <v>94580.340012330009</v>
+      </c>
+      <c r="F28" s="4">
+        <v>4.1181927359240046E-3</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2.9431664964802489E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="3">
+        <f>AVERAGE(D25:D26)</f>
+        <v>2184401.2981363921</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" ref="E30:G30" si="3">AVERAGE(E25:E26)</f>
+        <v>35363.114286409997</v>
+      </c>
+      <c r="F30" s="5">
+        <f t="shared" si="3"/>
+        <v>6.5395510904125943E-3</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" si="3"/>
+        <v>1.718012772163393E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3">
+        <f>AVERAGE(D27:D28)</f>
+        <v>1471697.1170046693</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" ref="E31:G31" si="4">AVERAGE(E27:E28)</f>
+        <v>85801.766245514998</v>
+      </c>
+      <c r="F31" s="5">
+        <f t="shared" si="4"/>
+        <v>6.8023244032194442E-3</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" si="4"/>
+        <v>3.0002098871263244E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="3">
+        <f>D30/D31</f>
+        <v>1.4842736816541999</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" ref="E33:G33" si="5">E30/E31</f>
+        <v>0.4121490248256805</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="5"/>
+        <v>0.96137007040086431</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57263086143914699</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <f>MAX(C25:C28)</f>
+        <v>4</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" ref="D35:G35" si="6">MAX(D25:D28)</f>
+        <v>2312764.5271400302</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="6"/>
+        <v>94580.340012330009</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="6"/>
+        <v>9.4864560705148846E-3</v>
+      </c>
+      <c r="G35" s="2">
+        <f t="shared" si="6"/>
+        <v>3.0572532777723999E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C36" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <f>C25/C$35</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" ref="D37:G37" si="7">D25/D$35</f>
+        <v>1</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.37449706271284755</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.59247665944601891</v>
+      </c>
+      <c r="G37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.61705446414673482</v>
+      </c>
+      <c r="I37" s="8">
+        <v>71</v>
+      </c>
+      <c r="J37" s="9">
+        <v>0.78951133158097364</v>
+      </c>
+      <c r="K37" s="9">
+        <v>0.6713484394542768</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C38" s="2">
+        <f t="shared" ref="C38:G40" si="8">C26/C$35</f>
+        <v>0.75</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.88899585107146872</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.3732928962109599</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.78623653793827153</v>
+      </c>
+      <c r="G38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.50683853134311552</v>
+      </c>
+      <c r="I38" s="8">
+        <v>72</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0.8324968816768088</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0.6782776485756381</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C39" s="2">
+        <f t="shared" si="8"/>
+        <v>0.5</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="8"/>
+        <v>0.74071957251902487</v>
+      </c>
+      <c r="E39" s="2">
+        <f t="shared" si="8"/>
+        <v>0.81436789578742097</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="I39" s="8">
+        <v>73</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0.90690785588122536</v>
+      </c>
+      <c r="K39" s="3">
+        <v>0.29242266909845338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C40" s="2">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="8"/>
+        <v>0.53195397442833625</v>
+      </c>
+      <c r="E40" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" si="8"/>
+        <v>0.4341128768543896</v>
+      </c>
+      <c r="G40" s="2">
+        <f t="shared" si="8"/>
+        <v>0.96268324181002174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="3">
+        <f>AVERAGE(J37:J39)</f>
+        <v>0.84297202304633601</v>
+      </c>
+      <c r="K41" s="3">
+        <f>AVERAGE(K37:K39)</f>
+        <v>0.54734958570945613</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C42" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C43" s="3">
+        <v>0.53195397442833625</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0.4341128768543896</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.96268324181002174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C44" s="3">
+        <v>0.74071957251902487</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.81436789578742097</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C45" s="3">
+        <v>0.88899585107146872</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.3732928962109599</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.78623653793827153</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0.50683853134311552</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.37449706271284755</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.59247665944601891</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0.50683853134311552</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2">
+        <v>3</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1177149.00870383</v>
+      </c>
+      <c r="E49" s="3">
+        <v>54257.120220599987</v>
+      </c>
+      <c r="F49" s="4">
+        <v>3.1222927114860181E-2</v>
+      </c>
+      <c r="G49" s="4">
+        <v>4.4066793598312361E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="2">
+        <v>4</v>
+      </c>
+      <c r="D50" s="3">
+        <v>1104497.8864203531</v>
+      </c>
+      <c r="E50" s="3">
+        <v>55926.329561999992</v>
+      </c>
+      <c r="F50" s="4">
+        <v>1.456969533637424E-2</v>
+      </c>
+      <c r="G50" s="4">
+        <v>1.725521704280945E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3">
+        <v>1083208.9167629869</v>
+      </c>
+      <c r="E51" s="3">
+        <v>110639.49239553</v>
+      </c>
+      <c r="F51" s="4">
+        <v>6.9333248439685724E-3</v>
+      </c>
+      <c r="G51" s="4">
+        <v>1.1143475296256969E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="2">
+        <v>2</v>
+      </c>
+      <c r="D52" s="3">
+        <v>1077864.821598877</v>
+      </c>
+      <c r="E52" s="3">
+        <v>73997.227386940009</v>
+      </c>
+      <c r="F52" s="4">
+        <v>9.7692142174449353E-3</v>
+      </c>
+      <c r="G52" s="4">
+        <v>9.558347653642385E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="3">
+        <f>AVERAGE(D49:D50)</f>
+        <v>1140823.4475620915</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" ref="E54:G54" si="9">AVERAGE(E49:E50)</f>
+        <v>55091.724891299993</v>
+      </c>
+      <c r="F54" s="5">
+        <f t="shared" si="9"/>
+        <v>2.2896311225617211E-2</v>
+      </c>
+      <c r="G54" s="5">
+        <f t="shared" si="9"/>
+        <v>3.0661005320560906E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B55" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="3">
+        <f>AVERAGE(D51:D52)</f>
+        <v>1080536.8691809319</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" ref="E55:G55" si="10">AVERAGE(E51:E52)</f>
+        <v>92318.359891235013</v>
+      </c>
+      <c r="F55" s="5">
+        <f t="shared" si="10"/>
+        <v>8.3512695307067543E-3</v>
+      </c>
+      <c r="G55" s="5">
+        <f t="shared" si="10"/>
+        <v>5.3363475916340412E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3">
+        <f>D54/D55</f>
+        <v>1.0557931710621387</v>
+      </c>
+      <c r="E57" s="3">
+        <f t="shared" ref="E57:G57" si="11">E54/E55</f>
+        <v>0.59675805501967727</v>
+      </c>
+      <c r="F57" s="3">
+        <f t="shared" si="11"/>
+        <v>2.741656360321008</v>
+      </c>
+      <c r="G57" s="3">
+        <f t="shared" si="11"/>
+        <v>0.57456911856021375</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C59" s="2">
+        <f>MAX(C49:C52)</f>
+        <v>4</v>
+      </c>
+      <c r="D59" s="2">
+        <f t="shared" ref="D59:G59" si="12">MAX(D49:D52)</f>
+        <v>1177149.00870383</v>
+      </c>
+      <c r="E59" s="2">
+        <f t="shared" si="12"/>
+        <v>110639.49239553</v>
+      </c>
+      <c r="F59" s="2">
+        <f t="shared" si="12"/>
+        <v>3.1222927114860181E-2</v>
+      </c>
+      <c r="G59" s="2">
+        <f t="shared" si="12"/>
+        <v>9.558347653642385E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C60" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="2">
+        <f t="shared" ref="C61:G64" si="13">C49/C$59</f>
+        <v>0.75</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="13"/>
+        <v>0.490395599670991</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="13"/>
+        <v>0.46102940795964764</v>
+      </c>
+      <c r="J61" s="8">
+        <v>71</v>
+      </c>
+      <c r="K61" s="3">
+        <f>0.5*(D46*E46+E46*F46+F46*G46+G46*D46)</f>
+        <v>0.70175318133655629</v>
+      </c>
+      <c r="L61" s="3">
+        <f>0.5*(D43*E43+E43*F43+F43*G43+G43*D43)</f>
+        <v>0.6713484394542768</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C62" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.93828213612185452</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.50548252121463544</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.46663451132485162</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.18052510400407995</v>
+      </c>
+      <c r="J62" s="8"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.25</v>
+      </c>
+      <c r="D63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.92019694087473147</v>
+      </c>
+      <c r="E63" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="F63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.22205877169885008</v>
+      </c>
+      <c r="G63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.11658369940133473</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="D64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.91565707793079165</v>
+      </c>
+      <c r="E64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.66881387273907633</v>
+      </c>
+      <c r="F64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.31288591814299799</v>
+      </c>
+      <c r="G64" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C66" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="3">
+        <v>0.91565707793079165</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.66881387273907633</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0.31288591814299799</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C68" s="3">
+        <v>0.92019694087473147</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E68" s="2">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0.22205877169885008</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0.11658369940133473</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C69" s="3">
+        <v>0.93828213612185452</v>
+      </c>
+      <c r="D69" s="2">
+        <v>1</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.50548252121463544</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0.46663451132485162</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0.18052510400407995</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C70" s="3">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.490395599670991</v>
+      </c>
+      <c r="F70" s="2">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2">
+        <v>0.46102940795964764</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="2">
+        <v>4</v>
+      </c>
+      <c r="D73" s="3">
+        <v>729412.67096789309</v>
+      </c>
+      <c r="E73" s="3">
+        <v>60313.34351775</v>
+      </c>
+      <c r="F73" s="4">
+        <v>3.7694938920620688E-4</v>
+      </c>
+      <c r="G73" s="4">
+        <v>1.654533485954597E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3">
+        <v>648447.24948227091</v>
+      </c>
+      <c r="E74" s="3">
+        <v>22130.276711350001</v>
+      </c>
+      <c r="F74" s="4">
+        <v>1.068848483528837E-2</v>
+      </c>
+      <c r="G74" s="4">
+        <v>8.5913209572516789E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="2">
+        <v>3</v>
+      </c>
+      <c r="D75" s="3">
+        <v>647963.01508706179</v>
+      </c>
+      <c r="E75" s="3">
+        <v>30679.58334573</v>
+      </c>
+      <c r="F75" s="4">
+        <v>6.9744795028248326E-4</v>
+      </c>
+      <c r="G75" s="4">
+        <v>1.104087647419581E-4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="2">
+        <v>2</v>
+      </c>
+      <c r="D76" s="3">
+        <v>585416.38894337451</v>
+      </c>
+      <c r="E76" s="3">
+        <v>80201.013479729998</v>
+      </c>
+      <c r="F76" s="4">
+        <v>3.0546519921711193E-4</v>
+      </c>
+      <c r="G76" s="4">
+        <v>1.7612261076438901E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="3">
+        <f>AVERAGE(D73:D74)</f>
+        <v>688929.960225082</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" ref="E78:G78" si="14">AVERAGE(E73:E74)</f>
+        <v>41221.810114549997</v>
+      </c>
+      <c r="F78" s="5">
+        <f t="shared" si="14"/>
+        <v>5.5327171122472882E-3</v>
+      </c>
+      <c r="G78" s="5">
+        <f t="shared" si="14"/>
+        <v>1.2568327908398826E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="3">
+        <f>AVERAGE(D75:D76)</f>
+        <v>616689.70201521809</v>
+      </c>
+      <c r="E79" s="3">
+        <f t="shared" ref="E79:G79" si="15">AVERAGE(E75:E76)</f>
+        <v>55440.298412730001</v>
+      </c>
+      <c r="F79" s="5">
+        <f t="shared" si="15"/>
+        <v>5.0145657474979762E-4</v>
+      </c>
+      <c r="G79" s="5">
+        <f t="shared" si="15"/>
+        <v>1.4326568775317356E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="3">
+        <f>D78/D79</f>
+        <v>1.1171419888702492</v>
+      </c>
+      <c r="E81" s="3">
+        <f t="shared" ref="E81:G81" si="16">E78/E79</f>
+        <v>0.74353514130949905</v>
+      </c>
+      <c r="F81" s="3">
+        <f t="shared" si="16"/>
+        <v>11.033292593696363</v>
+      </c>
+      <c r="G81" s="3">
+        <f t="shared" si="16"/>
+        <v>8.7727411256017351</v>
+      </c>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="2">
+        <f>MAX(C73:C76)</f>
+        <v>4</v>
+      </c>
+      <c r="D83" s="2">
+        <f t="shared" ref="D83:G83" si="17">MAX(D73:D76)</f>
+        <v>729412.67096789309</v>
+      </c>
+      <c r="E83" s="2">
+        <f t="shared" si="17"/>
+        <v>80201.013479729998</v>
+      </c>
+      <c r="F83" s="2">
+        <f t="shared" si="17"/>
+        <v>1.068848483528837E-2</v>
+      </c>
+      <c r="G83" s="2">
+        <f t="shared" si="17"/>
+        <v>1.654533485954597E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C84" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J84" s="2"/>
+      <c r="K84" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L84" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="2">
+        <f t="shared" ref="C85:G88" si="18">C73/C$83</f>
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="E85" s="2">
+        <f t="shared" si="18"/>
+        <v>0.75202719892054226</v>
+      </c>
+      <c r="F85" s="2">
+        <f t="shared" si="18"/>
+        <v>3.5266868505225042E-2</v>
+      </c>
+      <c r="G85" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="J85" s="8">
+        <v>72</v>
+      </c>
+      <c r="K85" s="3">
+        <f>0.5*(D70*E70+E70*F70+F70*G70+G70*D70)</f>
+        <v>0.8324968816768088</v>
+      </c>
+      <c r="L85" s="3">
+        <f>0.5*(D67*E67+E67*F67+F67*G67+G67*D67)</f>
+        <v>0.6782776485756381</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C86" s="2">
+        <f t="shared" si="18"/>
+        <v>0.25</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" si="18"/>
+        <v>0.88899915684466346</v>
+      </c>
+      <c r="E86" s="2">
+        <f t="shared" si="18"/>
+        <v>0.27593512539518228</v>
+      </c>
+      <c r="F86" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="G86" s="2">
+        <f t="shared" si="18"/>
+        <v>0.51925941845140988</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="2">
+        <f t="shared" si="18"/>
+        <v>0.75</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="18"/>
+        <v>0.88833528793412408</v>
+      </c>
+      <c r="E87" s="2">
+        <f t="shared" si="18"/>
+        <v>0.38253361166668992</v>
+      </c>
+      <c r="F87" s="2">
+        <f t="shared" si="18"/>
+        <v>6.5252274857502429E-2</v>
+      </c>
+      <c r="G87" s="2">
+        <f t="shared" si="18"/>
+        <v>6.6731054813470178E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="2">
+        <f t="shared" si="18"/>
+        <v>0.5</v>
+      </c>
+      <c r="D88" s="2">
+        <f t="shared" si="18"/>
+        <v>0.80258598766396128</v>
+      </c>
+      <c r="E88" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="F88" s="2">
+        <f t="shared" si="18"/>
+        <v>2.8578905609577977E-2</v>
+      </c>
+      <c r="G88" s="2">
+        <f t="shared" si="18"/>
+        <v>0.10644850180398349</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C90" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C91" s="3">
+        <v>0.80258598766396128</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E91" s="2">
+        <v>1</v>
+      </c>
+      <c r="F91" s="2">
+        <v>2.8578905609577977E-2</v>
+      </c>
+      <c r="G91" s="2">
+        <v>0.10644850180398349</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C92" s="3">
+        <v>0.88833528793412408</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.38253361166668992</v>
+      </c>
+      <c r="F92" s="2">
+        <v>6.5252274857502429E-2</v>
+      </c>
+      <c r="G92" s="2">
+        <v>6.6731054813470178E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C93" s="3">
+        <v>0.88899915684466346</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.27593512539518228</v>
+      </c>
+      <c r="F93" s="2">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2">
+        <v>0.51925941845140988</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2">
+        <v>1</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0.75202719892054226</v>
+      </c>
+      <c r="F94" s="2">
+        <v>3.5266868505225042E-2</v>
+      </c>
+      <c r="G94" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J108" s="2"/>
+      <c r="K108" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L108" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J109" s="8">
+        <v>73</v>
+      </c>
+      <c r="K109" s="3">
+        <f>0.5*(D94*E94+E94*F94+F94*G94+G94*D94)</f>
+        <v>0.90690785588122536</v>
+      </c>
+      <c r="L109" s="3">
+        <f>0.5*(D91*E91+E91*F91+F91*G91+G91*D91)</f>
+        <v>0.29242266909845338</v>
+      </c>
+    </row>
+    <row r="110" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J110" s="2"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+    </row>
+    <row r="111" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J111" s="8"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25:D28">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:E28">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25:F28">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25:G28">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:D31">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30:E31">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:F31">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G31">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D49:D52">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E49:E52">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F49:F52">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G49:G52">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D54:D55">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E54:E55">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F54:F55">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G54:G55">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D73:D76">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E73:E76">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F73:F76">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G73:G76">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D78:D79">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E78:E79">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F78:F79">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G78:G79">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/clustering/sepsectors/research sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/research sector (VDS_s) 0.xlsx
@@ -255,7 +255,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -559,7 +558,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -665,7 +663,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -969,7 +966,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1075,7 +1071,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1379,7 +1374,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1550,13 +1544,6 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sheet1 (2)'!$E$42:$G$42</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
@@ -1574,13 +1561,6 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sheet1 (2)'!$E$43:$G$43</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>'Sheet1 (2)'!$E$43:$G$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
@@ -1604,170 +1584,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Sheet1 (2)'!$C$44</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,74</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sheet1 (2)'!$E$42:$G$42</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sheet1 (2)'!$E$44:$G$44</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sheet1 (2)'!$E$44:$G$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.81436789578742097</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4942-4BDF-B4CA-C15D8E5F257C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Sheet1 (2)'!$C$45</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,89</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sheet1 (2)'!$E$42:$G$42</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sheet1 (2)'!$E$45:$G$45</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sheet1 (2)'!$E$45:$G$45</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.3732928962109599</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.78623653793827153</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.50683853134311552</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4942-4BDF-B4CA-C15D8E5F257C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Sheet1 (2)'!$C$46</c:f>
@@ -1793,13 +1611,6 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sheet1 (2)'!$E$42:$G$42</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>'Sheet1 (2)'!$E$42:$G$42</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
@@ -1817,13 +1628,6 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sheet1 (2)'!$E$46:$G$46</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>'Sheet1 (2)'!$E$46:$G$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
